--- a/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/observations-summary.xlsx
+++ b/stufe-5/organspendedetektion/feature-init-draft-PTDATA-1927/observations-summary.xlsx
@@ -68,7 +68,7 @@
     <t>dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>CodeableConceptĵ</t>
+    <t>CodeableConceptĵ, dateTimeĵ</t>
   </si>
   <si>
     <t>optional</t>
